--- a/src/main/resources/TestCases/Userstory3_EndToEnd.xlsx
+++ b/src/main/resources/TestCases/Userstory3_EndToEnd.xlsx
@@ -44,16 +44,16 @@
     <t>E2E: Full Hiring Lifecycle with Multiple Jobs, Candidates and Cascading Selections</t>
   </si>
   <si>
-    <t>End-to-end hiring lifecycle: Admin/Recruiter/Candidate registration, multiple job creations, multi-job applications, duplicate prevention, multi-stage status updates, cascading selection (selected=SELECTED, others=REJECTED, job=deactivated), cross-job isolation, multi-recruiter independence, post-closure blocking, job deletion and admin user deletion with auth verification</t>
-  </si>
-  <si>
-    <t>Register Admin user: POST http://localhost:5000/api/auth/register</t>
+    <t>End-to-end hiring lifecycle: Admin/Recruiter/Candidate registration, multiple job creations, multi-job applications, duplicate prevention, multi-stage status updates, cascading selection (ACCEPTED triggers auto-rejection of remaining applicants and job deactivation), cross-job isolation, multi-recruiter independence, post-closure blocking, job deletion and admin user deletion with auth verification</t>
+  </si>
+  <si>
+    <t>Register Admin1 user: POST http://localhost:5000/api/auth/register</t>
   </si>
   <si>
     <t>{
   "email": "admin@test.com",
   "password": "admin123",
-  "fullName": "Admin User",
+  "fullName": "Admin1",
   "phone": "9000000001",
   "role": "ADMIN"
 }</t>
@@ -65,7 +65,7 @@
   "data": {
     "id": 1,
     "email": "admin@test.com",
-    "fullName": "Admin User",
+    "fullName": "Admin1",
     "role": "ADMIN"
   }
 }</t>
@@ -74,13 +74,13 @@
     <t/>
   </si>
   <si>
-    <t>Register Recruiter 1 (Jaydeep): POST http://localhost:5000/api/auth/register</t>
+    <t>Register Recruiter1: POST http://localhost:5000/api/auth/register</t>
   </si>
   <si>
     <t>{
   "email": "jaydeep@test.com",
   "password": "pass123",
-  "fullName": "Jaydeep Recruiter",
+  "fullName": "Recruiter1",
   "phone": "9000000002",
   "role": "RECRUITER"
 }</t>
@@ -92,19 +92,19 @@
   "data": {
     "id": 2,
     "email": "jaydeep@test.com",
-    "fullName": "Jaydeep Recruiter",
+    "fullName": "Recruiter1",
     "role": "RECRUITER"
   }
 }</t>
   </si>
   <si>
-    <t>Register Recruiter 2 (Smitha): POST http://localhost:5000/api/auth/register</t>
+    <t>Register Recruiter2: POST http://localhost:5000/api/auth/register</t>
   </si>
   <si>
     <t>{
   "email": "smitha@test.com",
   "password": "pass123",
-  "fullName": "Smitha Recruiter",
+  "fullName": "Recruiter2",
   "phone": "9000000003",
   "role": "RECRUITER"
 }</t>
@@ -116,33 +116,39 @@
   "data": {
     "id": 3,
     "email": "smitha@test.com",
-    "fullName": "Smitha Recruiter",
+    "fullName": "Recruiter2",
     "role": "RECRUITER"
   }
 }</t>
   </si>
   <si>
-    <t>Register Candidate 1 (Manik), Candidate 2 (Prajwal), Candidate 3 (Omkar): POST http://localhost:5000/api/auth/register (x3)</t>
+    <t>Register Candidate1, Candidate2, Candidate3: POST http://localhost:5000/api/auth/register (x3)</t>
   </si>
   <si>
     <t>{
   "email": "manik@test.com",
   "password": "pass123",
-  "fullName": "Manik Candidate",
+  "fullName": "Candidate1",
   "phone": "9000000004",
   "role": "CANDIDATE"
-}</t>
+}
+// Repeated for prajwal@test.com (Candidate2) and omkar@test.com (Candidate3)</t>
   </si>
   <si>
     <t>{
   "success": true,
   "message": "User registered successfully",
-  "data": { "id": 4, "email": "manik@test.com", "fullName": "Manik Candidate", "role": "CANDIDATE" }
+  "data": {
+    "id": 4,
+    "email": "manik@test.com",
+    "fullName": "Candidate1",
+    "role": "CANDIDATE"
+  }
 }
 // Repeated for prajwal@test.com (id=5) and omkar@test.com (id=6)</t>
   </si>
   <si>
-    <t>Admin logs in and views all registered users: GET http://localhost:5000/api/admin/users</t>
+    <t>Admin1 logs in and views all registered users: GET http://localhost:5000/api/admin/users</t>
   </si>
   <si>
     <t>{
@@ -164,7 +170,7 @@
 }</t>
   </si>
   <si>
-    <t>Recruiter 1 (Jaydeep) logs in and creates Job 1 (Backend Engineer): POST http://localhost:5000/api/jobs</t>
+    <t>Recruiter1 logs in and creates Job1 (Backend Engineer): POST http://localhost:5000/api/jobs</t>
   </si>
   <si>
     <t>{
@@ -189,7 +195,7 @@
 }</t>
   </si>
   <si>
-    <t>Recruiter 1 creates Job 2 (Frontend Developer): POST http://localhost:5000/api/jobs</t>
+    <t>Recruiter1 creates Job2 (Frontend Developer): POST http://localhost:5000/api/jobs</t>
   </si>
   <si>
     <t>{
@@ -214,7 +220,7 @@
 }</t>
   </si>
   <si>
-    <t>Recruiter 2 (Smitha) logs in and creates Job 3 (Data Analyst): POST http://localhost:5000/api/jobs</t>
+    <t>Recruiter2 logs in and creates Job3 (Data Analyst): POST http://localhost:5000/api/jobs</t>
   </si>
   <si>
     <t>{
@@ -256,14 +262,14 @@
 }</t>
   </si>
   <si>
-    <t>Candidate 1 (Manik) applies to Job 1 and Job 2 simultaneously: POST http://localhost:5000/api/applications (x2)</t>
+    <t>Candidate1 applies to Job1 and Job2 simultaneously: POST http://localhost:5000/api/applications (x2)</t>
   </si>
   <si>
     <t>{
   "jobId": 1,
-  "coverLetter": "Manik applying for Backend Engineer at CloudNine."
+  "coverLetter": "Candidate1 applying for Backend Engineer at CloudNine."
 }
-// Then: { "jobId": 2, "coverLetter": "Manik applying for Frontend Developer at CloudNine." }</t>
+// Then: { "jobId": 2, "coverLetter": "Candidate1 applying for Frontend Developer at CloudNine." }</t>
   </si>
   <si>
     <t>{
@@ -280,7 +286,7 @@
 // Application id=2: jobId=2, status=PENDING</t>
   </si>
   <si>
-    <t>Candidate 1 (Manik) attempts duplicate apply to Job 1 — expects 409 Conflict: POST http://localhost:5000/api/applications</t>
+    <t>Candidate1 attempts duplicate apply to Job1 - expects 409 Conflict: POST http://localhost:5000/api/applications</t>
   </si>
   <si>
     <t>{
@@ -296,14 +302,14 @@
 }</t>
   </si>
   <si>
-    <t>Candidate 2 (Prajwal) applies to Job 1 and Job 3; Candidate 3 (Omkar) applies to Job 2 and Job 3: POST http://localhost:5000/api/applications (x4)</t>
+    <t>Candidate2 applies to Job1 and Job3; Candidate3 applies to Job2 and Job3: POST http://localhost:5000/api/applications (x4)</t>
   </si>
   <si>
     <t>{
   "jobId": 1,
-  "coverLetter": "Prajwal applying for Backend Engineer."
+  "coverLetter": "Candidate2 applying for Backend Engineer."
 }
-// Prajwal also: jobId=3 | Omkar: jobId=2, jobId=3</t>
+// Candidate2 also: jobId=3 | Candidate3: jobId=2, jobId=3</t>
   </si>
   <si>
     <t>{
@@ -318,7 +324,7 @@
 }</t>
   </si>
   <si>
-    <t>Recruiter 1 views applications for Job 1 only (isolation check): GET http://localhost:5000/api/applications/job/1</t>
+    <t>Recruiter1 views applications for Job1 only (isolation check): GET http://localhost:5000/api/applications/job/1</t>
   </si>
   <si>
     <t>http://localhost:5000/api/applications/job/1</t>
@@ -334,22 +340,22 @@
 }</t>
   </si>
   <si>
-    <t>Recruiter 1 updates Manik's Job 1 application to INTERVIEW_SCHEDULED, Prajwal's to ON_HOLD: PUT http://localhost:5000/api/applications/{id}/status</t>
-  </si>
-  <si>
-    <t>http://localhost:5000/api/applications/1/status?status=INTERVIEW_SCHEDULED
-// Then: http://localhost:5000/api/applications/3/status?status=ON_HOLD</t>
+    <t>Recruiter1 updates Candidate1 Job1 application to SHORTLISTED, Candidate2 to REVIEWED: PUT http://localhost:5000/api/applications/{id}/status</t>
+  </si>
+  <si>
+    <t>http://localhost:5000/api/applications/1/status?status=SHORTLISTED
+// Then: http://localhost:5000/api/applications/3/status?status=REVIEWED</t>
   </si>
   <si>
     <t>{
   "success": true,
   "message": "Application status updated",
-  "data": { "id": 1, "status": "INTERVIEW_SCHEDULED", "candidate": { "email": "manik@test.com" } }
+  "data": { "id": 1, "status": "SHORTLISTED", "candidate": { "email": "manik@test.com" } }
 }
-// app id=3: status = ON_HOLD</t>
-  </si>
-  <si>
-    <t>Candidate 1 (Manik) verifies dashboard shows INTERVIEW_SCHEDULED for Job 1 and PENDING for Job 2 (real-time + cross-job isolation): GET http://localhost:5000/api/applications/my</t>
+// app id=3: status=REVIEWED</t>
+  </si>
+  <si>
+    <t>Candidate1 verifies dashboard shows SHORTLISTED for Job1 and PENDING for Job2 (real-time cross-job isolation): GET http://localhost:5000/api/applications/my</t>
   </si>
   <si>
     <t>{
@@ -359,7 +365,7 @@
     {
       "id": 1,
       "job": { "id": 1, "title": "Backend Engineer", "company": "CloudNine Technologies" },
-      "status": "INTERVIEW_SCHEDULED",
+      "status": "SHORTLISTED",
       "appliedAt": "2026-05-29T11:00:00.000"
     },
     {
@@ -372,29 +378,25 @@
 }</t>
   </si>
   <si>
-    <t>Recruiter 1 selects Manik for Job 1 — triggers auto-rejection of Prajwal and job deactivation: PUT http://localhost:5000/api/applications/1/status?status=SELECTED</t>
-  </si>
-  <si>
-    <t>http://localhost:5000/api/applications/1/status?status=SELECTED</t>
-  </si>
-  <si>
-    <t>{
-  "success": true,
-  "message": "Application status updated. Job closed and remaining applicants rejected.",
+    <t>Recruiter1 accepts Candidate1 for Job1 - remaining applicants auto-REJECTED, Job1 deactivated: PUT http://localhost:5000/api/applications/1/status?status=ACCEPTED</t>
+  </si>
+  <si>
+    <t>http://localhost:5000/api/applications/1/status?status=ACCEPTED</t>
+  </si>
+  <si>
+    <t>{
+  "success": true,
+  "message": "Application status updated",
   "data": {
     "id": 1,
     "candidate": { "id": 4, "email": "manik@test.com" },
-    "status": "SELECTED",
-    "job": {
-      "id": 1,
-      "title": "Backend Engineer",
-      "active": false
-    }
+    "status": "ACCEPTED",
+    "job": { "id": 1, "title": "Backend Engineer", "active": false }
   }
 }</t>
   </si>
   <si>
-    <t>Verify Prajwal auto-REJECTED for Job 1 and Job 1 deactivated; Manik's Job 2 still PENDING (cross-job isolation): GET http://localhost:5000/api/applications/job/1 + GET http://localhost:5000/api/jobs</t>
+    <t>Verify Candidate2 auto-REJECTED for Job1 and Job1 deactivated; Candidate1 Job2 still PENDING (cross-job isolation): GET http://localhost:5000/api/applications/job/1 + GET http://localhost:5000/api/jobs</t>
   </si>
   <si>
     <t>http://localhost:5000/api/applications/job/1
@@ -404,37 +406,33 @@
     <t>{
   "success": true,
   "data": [
-    { "id": 1, "candidate": { "email": "manik@test.com" }, "status": "SELECTED" },
+    { "id": 1, "candidate": { "email": "manik@test.com" }, "status": "ACCEPTED" },
     { "id": 3, "candidate": { "email": "prajwal@test.com" }, "status": "REJECTED" }
   ]
 }
-// GET /api/jobs: Job 1 no longer in active listings; Job 2 and Job 3 still active
-// Manik GET /api/applications/my: Job 1 = SELECTED, Job 2 = PENDING (unchanged)</t>
-  </si>
-  <si>
-    <t>Recruiter 2 (Smitha) independently selects Prajwal for Job 3 — cascading rejection of Omkar for Job 3, Job 3 deactivated: PUT http://localhost:5000/api/applications/4/status?status=SELECTED</t>
-  </si>
-  <si>
-    <t>http://localhost:5000/api/applications/4/status?status=SELECTED</t>
-  </si>
-  <si>
-    <t>{
-  "success": true,
-  "message": "Application status updated. Job closed and remaining applicants rejected.",
+// GET /api/jobs: Job1 no longer in active listings; Job2 and Job3 still active
+// Candidate1 GET /api/applications/my: Job1=ACCEPTED, Job2=PENDING (unchanged)</t>
+  </si>
+  <si>
+    <t>Recruiter2 independently accepts Candidate2 for Job3 - Candidate3 auto-REJECTED for Job3, Job3 deactivated: PUT http://localhost:5000/api/applications/4/status?status=ACCEPTED</t>
+  </si>
+  <si>
+    <t>http://localhost:5000/api/applications/4/status?status=ACCEPTED</t>
+  </si>
+  <si>
+    <t>{
+  "success": true,
+  "message": "Application status updated",
   "data": {
     "id": 4,
     "candidate": { "id": 5, "email": "prajwal@test.com" },
-    "status": "SELECTED",
-    "job": {
-      "id": 3,
-      "title": "Data Analyst",
-      "active": false
-    }
+    "status": "ACCEPTED",
+    "job": { "id": 3, "title": "Data Analyst", "active": false }
   }
 }</t>
   </si>
   <si>
-    <t>New candidate attempts to apply for closed Job 1 — expects 400 error: POST http://localhost:5000/api/applications</t>
+    <t>New candidate (Candidate3) attempts to apply for closed Job1 - expects 400 Bad Request: POST http://localhost:5000/api/applications</t>
   </si>
   <si>
     <t>{
@@ -450,7 +448,7 @@
 }</t>
   </si>
   <si>
-    <t>Recruiter 1 deletes Job 2 (Frontend Developer) — job removed from listings: DELETE http://localhost:5000/api/jobs/2</t>
+    <t>Recruiter1 deletes Job2 (Frontend Developer) - job removed from listings: DELETE http://localhost:5000/api/jobs/2</t>
   </si>
   <si>
     <t>http://localhost:5000/api/jobs/2</t>
@@ -462,7 +460,7 @@
 }</t>
   </si>
   <si>
-    <t>Verify Job 2 no longer in listings and no active jobs remain: GET http://localhost:5000/api/jobs</t>
+    <t>Verify Job2 no longer in listings and no active jobs remain: GET http://localhost:5000/api/jobs</t>
   </si>
   <si>
     <t>{
@@ -472,7 +470,7 @@
 }</t>
   </si>
   <si>
-    <t>Admin deletes Candidate 3 (Omkar): DELETE http://localhost:5000/api/admin/users/6</t>
+    <t>Admin1 deletes Candidate3 (omkar@test.com): DELETE http://localhost:5000/api/admin/users/6</t>
   </si>
   <si>
     <t>http://localhost:5000/api/admin/users/6</t>
@@ -484,7 +482,7 @@
 }</t>
   </si>
   <si>
-    <t>Verify deleted Candidate 3 (Omkar) can no longer authenticate: POST http://localhost:5000/api/auth/login</t>
+    <t>Verify deleted Candidate3 can no longer authenticate - expects 401 Unauthorized: POST http://localhost:5000/api/auth/login</t>
   </si>
   <si>
     <t>{
@@ -676,7 +674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" ht="105.0" customHeight="true">
+    <row r="5" ht="165.0" customHeight="true">
       <c r="A5" t="s" s="3">
         <v>14</v>
       </c>
@@ -952,7 +950,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" ht="210.0" customHeight="true">
+    <row r="17" ht="150.0" customHeight="true">
       <c r="A17" t="s" s="3">
         <v>14</v>
       </c>
@@ -998,7 +996,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="19" ht="210.0" customHeight="true">
+    <row r="19" ht="150.0" customHeight="true">
       <c r="A19" t="s" s="3">
         <v>14</v>
       </c>
